--- a/E_nassauiDemographicGrowthParameters.xlsx
+++ b/E_nassauiDemographicGrowthParameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosiemangan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A70030-7709-FF42-8B85-67D9AB7D89F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A12962A-AE3B-9C4E-9A6C-5D56C89791DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1300" windowWidth="27240" windowHeight="15940" activeTab="1" xr2:uid="{9854F379-A2E1-9C44-97BB-4C747EF890F5}"/>
+    <workbookView xWindow="1560" yWindow="1300" windowWidth="27240" windowHeight="15940" xr2:uid="{9854F379-A2E1-9C44-97BB-4C747EF890F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029" iterate="1" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,10 +42,20 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={5FE7041E-3CB1-A145-A7D7-E29BB9685B38}</author>
     <author>Dorothy Hayden (external)</author>
+    <author>tc={9751D3F6-B9D9-4649-AED7-4E5082256911}</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{29D2AA70-95AD-CE48-8524-A57F3CC251E3}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{5FE7041E-3CB1-A145-A7D7-E29BB9685B38}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Add a field for each day from 0 to the maximum day so the pivot table shows a value for each day.  See the bottom of this column.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{29D2AA70-95AD-CE48-8524-A57F3CC251E3}">
       <text>
         <r>
           <rPr>
@@ -69,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4C7F1411-0C59-9C45-9B63-DE5115E9398D}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{4C7F1411-0C59-9C45-9B63-DE5115E9398D}">
       <text>
         <r>
           <rPr>
@@ -100,6 +110,14 @@
           </rPr>
           <t>The number of eggs laid that result in females. This is calculated from the sex ratio</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="2" shapeId="0" xr:uid="{9751D3F6-B9D9-4649-AED7-4E5082256911}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    As you remove a mother and her offspring from the lifetable, move her offspring to the side and refresh the pivot table.  This will give you a correct value for the entire set before you paste into the life table.</t>
       </text>
     </comment>
   </commentList>
@@ -2899,7 +2917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4B1C415-2705-8847-9711-C1C7E5511EAE}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4B1C415-2705-8847-9711-C1C7E5511EAE}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="J1:K81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0" sumSubtotal="1">
@@ -3570,6 +3588,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D1" dT="2025-08-16T23:02:27.50" personId="{00D5823D-E0BF-3142-9F7E-5FF40C2E66B6}" id="{5FE7041E-3CB1-A145-A7D7-E29BB9685B38}">
+    <text>Add a field for each day from 0 to the maximum day so the pivot table shows a value for each day.  See the bottom of this column.</text>
+  </threadedComment>
+  <threadedComment ref="G2" dT="2025-08-16T22:59:34.93" personId="{00D5823D-E0BF-3142-9F7E-5FF40C2E66B6}" id="{9751D3F6-B9D9-4649-AED7-4E5082256911}">
+    <text>As you remove a mother and her offspring from the lifetable, move her offspring to the side and refresh the pivot table.  This will give you a correct value for the entire set before you paste into the life table.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="F1" dT="2025-08-16T22:12:59.54" personId="{00D5823D-E0BF-3142-9F7E-5FF40C2E66B6}" id="{4AB72F8C-5CD7-4249-B364-77A5B3F67FE8}">
     <text>mx is the per capita female offspring</text>
   </threadedComment>
@@ -3671,8 +3700,8 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <f t="shared" ref="F2:F33" si="0">(E2*0.81)</f>
+      <c r="G2">
+        <f>(E2*0.81)</f>
         <v>0</v>
       </c>
       <c r="J2" s="2">
@@ -3698,8 +3727,8 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
+      <c r="G3">
+        <f>(E3*0.81)</f>
         <v>0</v>
       </c>
       <c r="J3" s="3">
@@ -3725,8 +3754,8 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
+      <c r="G4">
+        <f>(E4*0.81)</f>
         <v>0</v>
       </c>
       <c r="J4" s="3">
@@ -3752,8 +3781,8 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+      <c r="G5">
+        <f>(E5*0.81)</f>
         <v>0</v>
       </c>
       <c r="J5" s="3">
@@ -3779,8 +3808,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
+      <c r="G6">
+        <f>(E6*0.81)</f>
         <v>0</v>
       </c>
       <c r="J6" s="3">
@@ -3806,8 +3835,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
+      <c r="G7">
+        <f>(E7*0.81)</f>
         <v>0</v>
       </c>
       <c r="J7" s="3">
@@ -3833,8 +3862,8 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
+      <c r="G8">
+        <f>(E8*0.81)</f>
         <v>0</v>
       </c>
       <c r="J8" s="3">
@@ -3860,8 +3889,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
+      <c r="G9">
+        <f>(E9*0.81)</f>
         <v>0</v>
       </c>
       <c r="J9" s="3">
@@ -3887,8 +3916,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
+      <c r="G10">
+        <f>(E10*0.81)</f>
         <v>0</v>
       </c>
       <c r="J10" s="3">
@@ -3914,8 +3943,8 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
+      <c r="G11">
+        <f>(E11*0.81)</f>
         <v>0.81</v>
       </c>
       <c r="J11" s="3">
@@ -3941,8 +3970,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
+      <c r="G12">
+        <f>(E12*0.81)</f>
         <v>0</v>
       </c>
       <c r="J12" s="3">
@@ -3968,8 +3997,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
+      <c r="G13">
+        <f>(E13*0.81)</f>
         <v>0</v>
       </c>
       <c r="J13" s="3">
@@ -3995,8 +4024,8 @@
       <c r="E14">
         <v>3</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
+      <c r="G14">
+        <f>(E14*0.81)</f>
         <v>2.4300000000000002</v>
       </c>
       <c r="J14" s="3">
@@ -4022,8 +4051,8 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
+      <c r="G15">
+        <f>(E15*0.81)</f>
         <v>0</v>
       </c>
       <c r="J15" s="3">
@@ -4049,8 +4078,8 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
+      <c r="G16">
+        <f>(E16*0.81)</f>
         <v>0</v>
       </c>
       <c r="J16" s="3">
@@ -4076,8 +4105,8 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
+      <c r="G17">
+        <f>(E17*0.81)</f>
         <v>0</v>
       </c>
       <c r="J17" s="3">
@@ -4103,8 +4132,8 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
+      <c r="G18">
+        <f>(E18*0.81)</f>
         <v>0.81</v>
       </c>
       <c r="J18" s="3">
@@ -4130,8 +4159,8 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
+      <c r="G19">
+        <f>(E19*0.81)</f>
         <v>0</v>
       </c>
       <c r="J19" s="3">
@@ -4157,8 +4186,8 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
+      <c r="G20">
+        <f>(E20*0.81)</f>
         <v>0</v>
       </c>
       <c r="J20" s="3">
@@ -4184,8 +4213,8 @@
       <c r="E21">
         <v>2</v>
       </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
+      <c r="G21">
+        <f>(E21*0.81)</f>
         <v>1.62</v>
       </c>
       <c r="J21" s="3">
@@ -4211,8 +4240,8 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
+      <c r="G22">
+        <f>(E22*0.81)</f>
         <v>0</v>
       </c>
       <c r="J22" s="3">
@@ -4238,8 +4267,8 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
+      <c r="G23">
+        <f>(E23*0.81)</f>
         <v>0</v>
       </c>
       <c r="J23" s="3">
@@ -4265,8 +4294,8 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
+      <c r="G24">
+        <f>(E24*0.81)</f>
         <v>0</v>
       </c>
       <c r="J24" s="3">
@@ -4292,8 +4321,8 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
+      <c r="G25">
+        <f>(E25*0.81)</f>
         <v>0</v>
       </c>
       <c r="J25" s="3">
@@ -4319,8 +4348,8 @@
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
+      <c r="G26">
+        <f>(E26*0.81)</f>
         <v>0</v>
       </c>
       <c r="J26" s="3">
@@ -4346,8 +4375,8 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
+      <c r="G27">
+        <f>(E27*0.81)</f>
         <v>0</v>
       </c>
       <c r="J27" s="3">
@@ -4373,8 +4402,8 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
+      <c r="G28">
+        <f>(E28*0.81)</f>
         <v>0</v>
       </c>
       <c r="J28" s="3">
@@ -4400,8 +4429,8 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
+      <c r="G29">
+        <f>(E29*0.81)</f>
         <v>0</v>
       </c>
       <c r="J29" s="3">
@@ -4427,8 +4456,8 @@
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
+      <c r="G30">
+        <f>(E30*0.81)</f>
         <v>0</v>
       </c>
       <c r="J30" s="3">
@@ -4454,8 +4483,8 @@
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
+      <c r="G31">
+        <f>(E31*0.81)</f>
         <v>0</v>
       </c>
       <c r="J31" s="3">
@@ -4481,8 +4510,8 @@
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
+      <c r="G32">
+        <f>(E32*0.81)</f>
         <v>0</v>
       </c>
       <c r="J32" s="3">
@@ -4508,8 +4537,8 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
+      <c r="G33">
+        <f>(E33*0.81)</f>
         <v>0</v>
       </c>
       <c r="J33" s="3">
@@ -4535,8 +4564,8 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34">
-        <f t="shared" ref="F34:F65" si="1">(E34*0.81)</f>
+      <c r="G34">
+        <f>(E34*0.81)</f>
         <v>0</v>
       </c>
       <c r="J34" s="3">
@@ -4562,8 +4591,8 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35">
-        <f t="shared" si="1"/>
+      <c r="G35">
+        <f>(E35*0.81)</f>
         <v>0</v>
       </c>
       <c r="J35" s="3">
@@ -4589,8 +4618,8 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36">
-        <f t="shared" si="1"/>
+      <c r="G36">
+        <f>(E36*0.81)</f>
         <v>0</v>
       </c>
       <c r="J36" s="3">
@@ -4616,8 +4645,8 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37">
-        <f t="shared" si="1"/>
+      <c r="G37">
+        <f>(E37*0.81)</f>
         <v>0</v>
       </c>
       <c r="J37" s="3">
@@ -4643,8 +4672,8 @@
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38">
-        <f t="shared" si="1"/>
+      <c r="G38">
+        <f>(E38*0.81)</f>
         <v>0</v>
       </c>
       <c r="J38" s="3">
@@ -4670,8 +4699,8 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39">
-        <f t="shared" si="1"/>
+      <c r="G39">
+        <f>(E39*0.81)</f>
         <v>0</v>
       </c>
       <c r="J39" s="3">
@@ -4697,8 +4726,8 @@
       <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40">
-        <f t="shared" si="1"/>
+      <c r="G40">
+        <f>(E40*0.81)</f>
         <v>0</v>
       </c>
       <c r="J40" s="3">
@@ -4724,8 +4753,8 @@
       <c r="E41">
         <v>0</v>
       </c>
-      <c r="F41">
-        <f t="shared" si="1"/>
+      <c r="G41">
+        <f>(E41*0.81)</f>
         <v>0</v>
       </c>
       <c r="J41" s="3">
@@ -4752,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F34:F65" si="0">(E42*0.81)</f>
         <v>0</v>
       </c>
       <c r="J42" s="3">
@@ -4779,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J43" s="3">
@@ -4806,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J44" s="3">
@@ -4833,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J45" s="3">
@@ -4860,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J46" s="3">
@@ -4887,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J47" s="3">
@@ -4914,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.81</v>
       </c>
       <c r="J48" s="3">
@@ -4941,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J49" s="3">
@@ -4968,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J50" s="3">
@@ -4995,7 +5024,7 @@
         <v>5</v>
       </c>
       <c r="F51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.0500000000000007</v>
       </c>
       <c r="J51" s="3">
@@ -5022,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J52" s="3">
@@ -5049,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J53" s="3">
@@ -5076,7 +5105,7 @@
         <v>4</v>
       </c>
       <c r="F54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.24</v>
       </c>
       <c r="J54" s="3">
@@ -5103,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J55" s="3">
@@ -5130,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J56" s="3">
@@ -5157,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J57" s="3">
@@ -5184,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J58" s="3">
@@ -5211,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J59" s="3">
@@ -5238,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J60" s="3">
@@ -5265,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J61" s="3">
@@ -5292,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J62" s="3">
@@ -5319,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J63" s="3">
@@ -5346,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J64" s="3">
@@ -5373,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J65" s="3">
@@ -5400,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <f t="shared" ref="F66:F97" si="2">(E66*0.81)</f>
+        <f t="shared" ref="F66:F81" si="1">(E66*0.81)</f>
         <v>0</v>
       </c>
       <c r="J66" s="3">
@@ -5427,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J67" s="3">
@@ -5454,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J68" s="3">
@@ -5481,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J69" s="3">
@@ -5508,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J70" s="3">
@@ -5535,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J71" s="3">
@@ -5562,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J72" s="3">
@@ -5589,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J73" s="3">
@@ -5616,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J74" s="3">
@@ -5643,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J75" s="3">
@@ -5670,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J76" s="3">
@@ -5697,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J77" s="3">
@@ -5724,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
@@ -5751,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
@@ -5778,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
@@ -5805,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J81" s="5" t="s">
@@ -5832,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <f t="shared" ref="F82:F145" si="3">(E82*0.81)</f>
+        <f t="shared" ref="F82:F145" si="2">(E82*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -5853,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5874,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5895,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5916,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5937,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5958,7 +5987,7 @@
         <v>3</v>
       </c>
       <c r="F88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
@@ -5979,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6000,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6021,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6042,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6063,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6084,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6105,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6126,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6147,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6168,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.81</v>
       </c>
     </row>
@@ -6189,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6210,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="F100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6231,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6252,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6273,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6294,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6315,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6336,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6357,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6378,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6399,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6420,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6441,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6462,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6483,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="F113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6504,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="F114">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6525,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6546,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6567,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6588,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6609,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6630,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6651,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="F121">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6672,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6693,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6714,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6735,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6756,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6777,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6798,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="F128">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.81</v>
       </c>
     </row>
@@ -6819,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6840,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6861,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6882,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6903,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6924,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6945,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6966,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="F136">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6987,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="F137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7008,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7029,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="F139">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7050,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7071,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7092,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7113,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7134,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7155,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="F145">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7176,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <f t="shared" ref="F146:F209" si="4">(E146*0.81)</f>
+        <f t="shared" ref="F146:F209" si="3">(E146*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -7197,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7218,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="F148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7239,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7260,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7281,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7302,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7323,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7344,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7365,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7386,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7407,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7428,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7449,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7470,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7491,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7512,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7533,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7554,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7575,7 +7604,7 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7596,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7617,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7638,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7659,7 +7688,7 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7680,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7701,7 +7730,7 @@
         <v>2</v>
       </c>
       <c r="F171">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.62</v>
       </c>
     </row>
@@ -7722,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="F172">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7743,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7764,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7785,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7806,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7827,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7848,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7869,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7890,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7911,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7932,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7953,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7974,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7995,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8016,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8037,7 +8066,7 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8058,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8079,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8100,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8121,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8142,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8163,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="F193">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8184,7 +8213,7 @@
         <v>0</v>
       </c>
       <c r="F194">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8205,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8226,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="F196">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8247,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8268,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8289,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="F199">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8310,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="F200">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8331,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="F201">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8352,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="F202">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8373,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8394,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8415,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="F205">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8436,7 +8465,7 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8457,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="F207">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8478,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="F208">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8499,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="F209">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8520,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="F210">
-        <f t="shared" ref="F210:F273" si="5">(E210*0.81)</f>
+        <f t="shared" ref="F210:F273" si="4">(E210*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -8541,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="F211">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8562,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="F212">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8583,7 +8612,7 @@
         <v>5</v>
       </c>
       <c r="F213">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.0500000000000007</v>
       </c>
     </row>
@@ -8604,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="F214">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8625,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="F215">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8646,7 +8675,7 @@
         <v>6</v>
       </c>
       <c r="F216">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.8600000000000003</v>
       </c>
     </row>
@@ -8667,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="F217">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8688,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="F218">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8709,7 +8738,7 @@
         <v>5</v>
       </c>
       <c r="F219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.0500000000000007</v>
       </c>
     </row>
@@ -8730,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="F220">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8751,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="F221">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8772,7 +8801,7 @@
         <v>6</v>
       </c>
       <c r="F222">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.8600000000000003</v>
       </c>
     </row>
@@ -8793,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="F223">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8814,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="F224">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8835,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="F225">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8856,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="F226">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8877,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="F227">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8898,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="F228">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8919,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="F229">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8940,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="F230">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.81</v>
       </c>
     </row>
@@ -8961,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="F231">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8982,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="F232">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9003,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="F233">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9024,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="F234">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9045,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="F235">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9066,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="F236">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9087,7 +9116,7 @@
         <v>0</v>
       </c>
       <c r="F237">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9108,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="F238">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9129,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="F239">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9150,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="F240">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9171,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="F241">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9192,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="F242">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9213,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="F243">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9234,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="F244">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9255,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="F245">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9276,7 +9305,7 @@
         <v>0</v>
       </c>
       <c r="F246">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9297,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="F247">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9318,7 +9347,7 @@
         <v>0</v>
       </c>
       <c r="F248">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9339,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="F249">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9360,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="F250">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9381,7 +9410,7 @@
         <v>3</v>
       </c>
       <c r="F251">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
@@ -9402,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="F252">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9423,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="F253">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9444,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="F254">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9465,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="F255">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9486,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="F256">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9507,7 +9536,7 @@
         <v>5</v>
       </c>
       <c r="F257">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.0500000000000007</v>
       </c>
     </row>
@@ -9528,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="F258">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9549,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="F259">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9570,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="F260">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9591,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="F261">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9612,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="F262">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9633,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="F263">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9654,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="F264">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9675,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="F265">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9696,7 +9725,7 @@
         <v>1</v>
       </c>
       <c r="F266">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.81</v>
       </c>
     </row>
@@ -9717,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="F267">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9738,7 +9767,7 @@
         <v>0</v>
       </c>
       <c r="F268">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9759,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="F269">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9780,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="F270">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9801,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="F271">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9822,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="F272">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9843,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="F273">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9864,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="F274">
-        <f t="shared" ref="F274:F337" si="6">(E274*0.81)</f>
+        <f t="shared" ref="F274:F337" si="5">(E274*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -9885,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="F275">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9906,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="F276">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9927,7 +9956,7 @@
         <v>0</v>
       </c>
       <c r="F277">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9948,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="F278">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9969,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="F279">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -9990,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="F280">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10011,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="F281">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10032,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="F282">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10053,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="F283">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10074,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="F284">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10095,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="F285">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10116,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="F286">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10137,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="F287">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.81</v>
       </c>
     </row>
@@ -10158,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="F288">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10179,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="F289">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10200,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="F290">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10221,7 +10250,7 @@
         <v>0</v>
       </c>
       <c r="F291">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10242,7 +10271,7 @@
         <v>0</v>
       </c>
       <c r="F292">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10263,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="F293">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.81</v>
       </c>
     </row>
@@ -10284,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="F294">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10305,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="F295">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10326,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="F296">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.81</v>
       </c>
     </row>
@@ -10347,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="F297">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10368,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="F298">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10389,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="F299">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10410,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="F300">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10431,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="F301">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10452,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="F302">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10473,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="F303">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10494,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="F304">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10515,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="F305">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.81</v>
       </c>
     </row>
@@ -10536,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="F306">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10557,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="F307">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10578,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="F308">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10599,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="F309">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10620,7 +10649,7 @@
         <v>0</v>
       </c>
       <c r="F310">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10641,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="F311">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10662,7 +10691,7 @@
         <v>3</v>
       </c>
       <c r="F312">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
@@ -10683,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="F313">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10704,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="F314">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10725,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="F315">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10746,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="F316">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10767,7 +10796,7 @@
         <v>0</v>
       </c>
       <c r="F317">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10788,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="F318">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10809,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="F319">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10830,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="F320">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10851,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="F321">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10872,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="F322">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10893,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="F323">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10914,7 +10943,7 @@
         <v>0</v>
       </c>
       <c r="F324">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10935,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="F325">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10956,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="F326">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -10977,7 +11006,7 @@
         <v>2</v>
       </c>
       <c r="F327">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.62</v>
       </c>
     </row>
@@ -10998,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="F328">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11019,7 +11048,7 @@
         <v>0</v>
       </c>
       <c r="F329">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11040,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="F330">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11061,7 +11090,7 @@
         <v>0</v>
       </c>
       <c r="F331">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11082,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="F332">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11103,7 +11132,7 @@
         <v>2</v>
       </c>
       <c r="F333">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.62</v>
       </c>
     </row>
@@ -11124,7 +11153,7 @@
         <v>0</v>
       </c>
       <c r="F334">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11145,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="F335">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11166,7 +11195,7 @@
         <v>0</v>
       </c>
       <c r="F336">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11187,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="F337">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11208,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="F338">
-        <f t="shared" ref="F338:F361" si="7">(E338*0.81)</f>
+        <f t="shared" ref="F338:F361" si="6">(E338*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -11229,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="F339">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11250,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="F340">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11271,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="F341">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11292,7 +11321,7 @@
         <v>0</v>
       </c>
       <c r="F342">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11313,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="F343">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11334,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="F344">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11355,7 +11384,7 @@
         <v>1</v>
       </c>
       <c r="F345">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.81</v>
       </c>
     </row>
@@ -11376,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="F346">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11397,7 +11426,7 @@
         <v>0</v>
       </c>
       <c r="F347">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11418,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="F348">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11439,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="F349">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11460,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="F350">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11481,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="F351">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11502,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="F352">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11523,7 +11552,7 @@
         <v>0</v>
       </c>
       <c r="F353">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11544,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="F354">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11565,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="F355">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11586,7 +11615,7 @@
         <v>0</v>
       </c>
       <c r="F356">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11607,7 +11636,7 @@
         <v>0</v>
       </c>
       <c r="F357">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11628,7 +11657,7 @@
         <v>0</v>
       </c>
       <c r="F358">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11649,7 +11678,7 @@
         <v>0</v>
       </c>
       <c r="F359">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11670,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="F360">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11691,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="F361">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -11712,7 +11741,7 @@
         <v>0</v>
       </c>
       <c r="F362">
-        <f t="shared" ref="F362:F403" si="8">(E362*0.81)</f>
+        <f t="shared" ref="F362:F403" si="7">(E362*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -11733,7 +11762,7 @@
         <v>0</v>
       </c>
       <c r="F363">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11754,7 +11783,7 @@
         <v>0</v>
       </c>
       <c r="F364">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11775,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="F365">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11796,7 +11825,7 @@
         <v>0</v>
       </c>
       <c r="F366">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11817,7 +11846,7 @@
         <v>3</v>
       </c>
       <c r="F367">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
@@ -11838,7 +11867,7 @@
         <v>0</v>
       </c>
       <c r="F368">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11859,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="F369">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11880,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="F370">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.81</v>
       </c>
     </row>
@@ -11901,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="F371">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11922,7 +11951,7 @@
         <v>0</v>
       </c>
       <c r="F372">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11943,7 +11972,7 @@
         <v>0</v>
       </c>
       <c r="F373">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11964,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="F374">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11985,7 +12014,7 @@
         <v>0</v>
       </c>
       <c r="F375">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12006,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="F376">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12027,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="F377">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12048,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="F378">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12069,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="F379">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12090,7 +12119,7 @@
         <v>0</v>
       </c>
       <c r="F380">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12111,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="F381">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12132,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="F382">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12153,7 +12182,7 @@
         <v>0</v>
       </c>
       <c r="F383">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12174,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="F384">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12195,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="F385">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12216,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="F386">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12237,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="F387">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12258,7 +12287,7 @@
         <v>0</v>
       </c>
       <c r="F388">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12279,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="F389">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12300,7 +12329,7 @@
         <v>0</v>
       </c>
       <c r="F390">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12321,7 +12350,7 @@
         <v>0</v>
       </c>
       <c r="F391">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12342,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="F392">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12363,7 +12392,7 @@
         <v>0</v>
       </c>
       <c r="F393">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12384,7 +12413,7 @@
         <v>0</v>
       </c>
       <c r="F394">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12405,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="F395">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12426,7 +12455,7 @@
         <v>0</v>
       </c>
       <c r="F396">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12447,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="F397">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12468,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="F398">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12489,7 +12518,7 @@
         <v>0</v>
       </c>
       <c r="F399">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12510,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="F400">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12531,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="F401">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12552,7 +12581,7 @@
         <v>0</v>
       </c>
       <c r="F402">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12573,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="F403">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -12582,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="F404">
-        <f t="shared" ref="F404:F442" si="9">(E404*0.81)</f>
+        <f t="shared" ref="F404:F442" si="8">(E404*0.81)</f>
         <v>0</v>
       </c>
     </row>
@@ -12591,7 +12620,7 @@
         <v>2</v>
       </c>
       <c r="F405">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12600,7 +12629,7 @@
         <v>3</v>
       </c>
       <c r="F406">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12609,7 +12638,7 @@
         <v>4</v>
       </c>
       <c r="F407">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12618,7 +12647,7 @@
         <v>5</v>
       </c>
       <c r="F408">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12627,7 +12656,7 @@
         <v>6</v>
       </c>
       <c r="F409">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12636,7 +12665,7 @@
         <v>7</v>
       </c>
       <c r="F410">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12645,7 +12674,7 @@
         <v>8</v>
       </c>
       <c r="F411">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12654,7 +12683,7 @@
         <v>9</v>
       </c>
       <c r="F412">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12663,7 +12692,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12672,7 +12701,7 @@
         <v>11</v>
       </c>
       <c r="F414">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12681,7 +12710,7 @@
         <v>12</v>
       </c>
       <c r="F415">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12690,7 +12719,7 @@
         <v>13</v>
       </c>
       <c r="F416">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12699,7 +12728,7 @@
         <v>14</v>
       </c>
       <c r="F417">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12708,7 +12737,7 @@
         <v>15</v>
       </c>
       <c r="F418">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12717,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="F419">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12726,7 +12755,7 @@
         <v>17</v>
       </c>
       <c r="F420">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12735,7 +12764,7 @@
         <v>18</v>
       </c>
       <c r="F421">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12744,7 +12773,7 @@
         <v>19</v>
       </c>
       <c r="F422">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12753,7 +12782,7 @@
         <v>20</v>
       </c>
       <c r="F423">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12762,7 +12791,7 @@
         <v>21</v>
       </c>
       <c r="F424">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12771,7 +12800,7 @@
         <v>22</v>
       </c>
       <c r="F425">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12780,7 +12809,7 @@
         <v>23</v>
       </c>
       <c r="F426">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12789,7 +12818,7 @@
         <v>24</v>
       </c>
       <c r="F427">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12798,7 +12827,7 @@
         <v>25</v>
       </c>
       <c r="F428">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12807,7 +12836,7 @@
         <v>26</v>
       </c>
       <c r="F429">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12816,7 +12845,7 @@
         <v>27</v>
       </c>
       <c r="F430">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12825,7 +12854,7 @@
         <v>28</v>
       </c>
       <c r="F431">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12834,7 +12863,7 @@
         <v>29</v>
       </c>
       <c r="F432">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12843,7 +12872,7 @@
         <v>30</v>
       </c>
       <c r="F433">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12852,7 +12881,7 @@
         <v>31</v>
       </c>
       <c r="F434">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12861,7 +12890,7 @@
         <v>32</v>
       </c>
       <c r="F435">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12870,7 +12899,7 @@
         <v>33</v>
       </c>
       <c r="F436">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12879,7 +12908,7 @@
         <v>34</v>
       </c>
       <c r="F437">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12888,7 +12917,7 @@
         <v>35</v>
       </c>
       <c r="F438">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12897,7 +12926,7 @@
         <v>36</v>
       </c>
       <c r="F439">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12906,7 +12935,7 @@
         <v>37</v>
       </c>
       <c r="F440">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12915,7 +12944,7 @@
         <v>38</v>
       </c>
       <c r="F441">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -12924,7 +12953,7 @@
         <v>39</v>
       </c>
       <c r="F442">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
